--- a/CampusGenie-backend/Genie-server/src/main/resources/template/KnowledgeBaseImportTemplate.xlsx
+++ b/CampusGenie-backend/Genie-server/src/main/resources/template/KnowledgeBaseImportTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pcuser\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0DB3332-DA9A-43C2-90EA-DBE50E1EA256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8AA611-A62A-469C-B774-D78ECEC630FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4D5B7B05-34F8-43B6-94C5-164E754ECB5A}"/>
   </bookViews>
@@ -16,9 +16,6 @@
     <sheet name="KnowlegdeBase" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">KnowlegdeBase!$A$1:$D$7</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,19 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>Column1</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>问题</t>
   </si>
@@ -114,9 +99,6 @@
     <t>校园卡丢失请立即挂失，方式一：登录校园卡服务中心网站挂失；方式二：在自助终端机上操作；方式三：到学生事务中心柜台办理。补卡费用20元。</t>
   </si>
   <si>
-    <t>校园卡事务</t>
-  </si>
-  <si>
     <t>学生手册</t>
   </si>
   <si>
@@ -127,6 +109,10 @@
   </si>
   <si>
     <t>宿舍生活</t>
+  </si>
+  <si>
+    <t>校园卡事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -172,11 +158,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -209,27 +192,14 @@
 </styleSheet>
 </file>
 
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{93D961EF-6DFC-403F-A949-351B0315FBD0}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="5">
-    <queryTableFields count="4">
-      <queryTableField id="1" name="Column1" tableColumnId="1"/>
-      <queryTableField id="2" name="Column2" tableColumnId="2"/>
-      <queryTableField id="3" name="Column3" tableColumnId="3"/>
-      <queryTableField id="4" name="Column4" tableColumnId="4"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA89691D-E483-49A4-8243-6C1C0C006230}" name="KnowlegdeBase" displayName="KnowlegdeBase" ref="A1:D7" tableType="queryTable" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AA89691D-E483-49A4-8243-6C1C0C006230}" name="KnowlegdeBase" displayName="KnowlegdeBase" ref="A1:D7" totalsRowShown="0">
   <autoFilter ref="A1:D7" xr:uid="{AA89691D-E483-49A4-8243-6C1C0C006230}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F7C830FE-9559-48F1-9274-F053759F5ABA}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{346D7EC8-7301-4490-AD7E-E12D11D56B2E}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{B986E319-0671-414C-9B1B-E2D943B1D138}" uniqueName="3" name="Column3" queryTableFieldId="3" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{558F2B13-054D-4B14-A13C-193C066C12E7}" uniqueName="4" name="Column4" queryTableFieldId="4" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F7C830FE-9559-48F1-9274-F053759F5ABA}" name="问题" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{346D7EC8-7301-4490-AD7E-E12D11D56B2E}" name="回答" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{B986E319-0671-414C-9B1B-E2D943B1D138}" name="分类" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{558F2B13-054D-4B14-A13C-193C066C12E7}" name="来源" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -532,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4FB2BE-9529-455A-9BD0-DF8978FE08FA}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
@@ -555,87 +525,73 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
+      <c r="D6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
